--- a/fixtures/sml/layout/auto-filter.xlsx
+++ b/fixtures/sml/layout/auto-filter.xlsx
@@ -10,16 +10,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>City</t>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Age</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Score</t>
-  </si>
-  <si>
-    <t>Age</t>
+    <t>City</t>
   </si>
 </sst>
 </file>
@@ -29,16 +29,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
